--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_18-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_18-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43607D72-EEC8-46C3-9ABB-D1B1D2455F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A93BBB-8850-4DC9-8A64-C3E89027225D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="1830" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32265" yWindow="1230" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1576,13 +1576,13 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
         <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
         <v>88</v>
